--- a/franquias/pwr_reports_mensal/KEYS Service Main Service Exceptions - Franquias (Stores)(2026-09-01 - 2026-09-06).xlsx
+++ b/franquias/pwr_reports_mensal/KEYS Service Main Service Exceptions - Franquias (Stores)(2026-09-01 - 2026-09-06).xlsx
@@ -875,34 +875,34 @@
     <t>174</t>
   </si>
   <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>R$ 38.374,88</t>
-  </si>
-  <si>
-    <t>408.9</t>
-  </si>
-  <si>
-    <t>259.9</t>
-  </si>
-  <si>
-    <t>6.37</t>
+    <t>135</t>
+  </si>
+  <si>
+    <t>R$ 40.126,32</t>
+  </si>
+  <si>
+    <t>427.5</t>
+  </si>
+  <si>
+    <t>271.4</t>
+  </si>
+  <si>
+    <t>6.41</t>
   </si>
   <si>
     <t>22.0</t>
   </si>
   <si>
-    <t>9.0</t>
+    <t>8.9</t>
   </si>
   <si>
     <t>6.5</t>
   </si>
   <si>
-    <t>29.8%</t>
-  </si>
-  <si>
-    <t>17.6%</t>
+    <t>29.5%</t>
+  </si>
+  <si>
+    <t>17.7%</t>
   </si>
   <si>
     <t>1.9%</t>
@@ -911,10 +911,10 @@
     <t>0.7%</t>
   </si>
   <si>
-    <t>4.4%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
+    <t>4.3%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -929,40 +929,40 @@
     <t>4.9%</t>
   </si>
   <si>
-    <t>8655.0</t>
-  </si>
-  <si>
-    <t>7040.0</t>
-  </si>
-  <si>
-    <t>764.0</t>
-  </si>
-  <si>
-    <t>270.0</t>
-  </si>
-  <si>
-    <t>1744.0</t>
-  </si>
-  <si>
-    <t>583.0</t>
-  </si>
-  <si>
-    <t>72.0</t>
-  </si>
-  <si>
-    <t>2442.0</t>
-  </si>
-  <si>
-    <t>902.0</t>
-  </si>
-  <si>
-    <t>1944.0</t>
+    <t>9075.0</t>
+  </si>
+  <si>
+    <t>7404.0</t>
+  </si>
+  <si>
+    <t>794.0</t>
+  </si>
+  <si>
+    <t>285.0</t>
+  </si>
+  <si>
+    <t>1790.0</t>
+  </si>
+  <si>
+    <t>604.0</t>
+  </si>
+  <si>
+    <t>79.0</t>
+  </si>
+  <si>
+    <t>2563.0</t>
+  </si>
+  <si>
+    <t>966.0</t>
+  </si>
+  <si>
+    <t>2067.0</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>204.0</t>
+    <t>212.0</t>
   </si>
   <si>
     <t>1</t>
@@ -3737,7 +3737,7 @@
         <v>19546</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C16" s="4">
         <v>51</v>
@@ -3768,40 +3768,40 @@
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="5">
-        <v>36729.520000000004</v>
+        <v>42513.350000000006</v>
       </c>
       <c r="N16" s="6">
-        <v>384</v>
+        <v>451</v>
       </c>
       <c r="O16" s="6">
-        <v>195</v>
+        <v>232</v>
       </c>
       <c r="P16" s="7">
-        <v>3.2341643044619421</v>
+        <v>3.1457216517857143</v>
       </c>
       <c r="Q16" s="8">
-        <v>20.419931443298967</v>
+        <v>19.9535354978355</v>
       </c>
       <c r="R16" s="8">
-        <v>10.230326804123711</v>
+        <v>9.8715221739130428</v>
       </c>
       <c r="S16" s="8">
         <v>7</v>
       </c>
       <c r="T16" s="9">
-        <v>0.27319587628865977</v>
+        <v>0.31601731601731603</v>
       </c>
       <c r="U16" s="9">
-        <v>0.16923076923076924</v>
+        <v>0.15948275862068967</v>
       </c>
       <c r="V16" s="9">
-        <v>0.0051282051282051282</v>
+        <v>0.0043103448275862068</v>
       </c>
       <c r="W16" s="9">
         <v>0</v>
       </c>
       <c r="X16" s="9">
-        <v>0.092307692307692313</v>
+        <v>0.086206896551724144</v>
       </c>
       <c r="Y16" s="9">
         <v>0</v>
@@ -3810,19 +3810,19 @@
         <v>0</v>
       </c>
       <c r="AA16" s="9">
-        <v>0.010256410256410256</v>
+        <v>0.012931034482758621</v>
       </c>
       <c r="AB16" s="9">
-        <v>0.010256410256410256</v>
+        <v>0.012931034482758621</v>
       </c>
       <c r="AC16" s="9">
-        <v>0.061538461538461542</v>
+        <v>0.051724137931034482</v>
       </c>
       <c r="AD16" s="6">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AE16" s="6">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AF16" s="6">
         <v>1</v>
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="AH16" s="6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI16" s="6">
         <v>0</v>
@@ -3840,10 +3840,10 @@
         <v>0</v>
       </c>
       <c r="AK16" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL16" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM16" s="6">
         <v>12</v>
@@ -3894,7 +3894,7 @@
         <v>19547</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C17" s="4">
         <v>51</v>
@@ -3925,61 +3925,61 @@
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="5">
-        <v>28554.010000000002</v>
+        <v>34644.370000000003</v>
       </c>
       <c r="N17" s="6">
-        <v>313</v>
+        <v>380</v>
       </c>
       <c r="O17" s="6">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="P17" s="7">
-        <v>9.7662446202531648</v>
+        <v>9.2736794805194798</v>
       </c>
       <c r="Q17" s="8">
-        <v>27.730701754385965</v>
+        <v>26.736949528301885</v>
       </c>
       <c r="R17" s="8">
-        <v>10.26343393939394</v>
+        <v>9.6316339805825244</v>
       </c>
       <c r="S17" s="8">
         <v>8</v>
       </c>
       <c r="T17" s="9">
-        <v>0.070175438596491224</v>
+        <v>0.080188679245283015</v>
       </c>
       <c r="U17" s="9">
-        <v>0.13450292397660818</v>
+        <v>0.17452830188679244</v>
       </c>
       <c r="V17" s="9">
-        <v>0.023391812865497075</v>
+        <v>0.018867924528301886</v>
       </c>
       <c r="W17" s="9">
         <v>0</v>
       </c>
       <c r="X17" s="9">
-        <v>0.0058479532163742687</v>
+        <v>0.0047169811320754715</v>
       </c>
       <c r="Y17" s="9">
         <v>0</v>
       </c>
       <c r="Z17" s="9">
-        <v>0.011695906432748537</v>
+        <v>0.018867924528301886</v>
       </c>
       <c r="AA17" s="9">
-        <v>0.040935672514619881</v>
+        <v>0.037735849056603772</v>
       </c>
       <c r="AB17" s="9">
-        <v>0.052631578947368418</v>
+        <v>0.051886792452830191</v>
       </c>
       <c r="AC17" s="9">
-        <v>0.011695906432748537</v>
+        <v>0.056603773584905662</v>
       </c>
       <c r="AD17" s="6">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AE17" s="6">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AF17" s="6">
         <v>4</v>
@@ -3994,16 +3994,16 @@
         <v>0</v>
       </c>
       <c r="AJ17" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AK17" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL17" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AM17" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -4522,7 +4522,7 @@
         <v>19553</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C21" s="4">
         <v>51</v>
@@ -4551,49 +4551,49 @@
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="5">
-        <v>38185.919999999998</v>
+        <v>51037.239999999998</v>
       </c>
       <c r="N21" s="6">
-        <v>347</v>
+        <v>471</v>
       </c>
       <c r="O21" s="6">
-        <v>240</v>
+        <v>309</v>
       </c>
       <c r="P21" s="7">
-        <v>8.2924793871866296</v>
+        <v>6.8723830578512395</v>
       </c>
       <c r="Q21" s="8">
-        <v>25.321042083333335</v>
+        <v>23.469310032362461</v>
       </c>
       <c r="R21" s="8">
-        <v>10.345168067226892</v>
+        <v>9.771162171052632</v>
       </c>
       <c r="S21" s="8">
         <v>7</v>
       </c>
       <c r="T21" s="9">
-        <v>0.25833333333333336</v>
+        <v>0.26860841423948217</v>
       </c>
       <c r="U21" s="9">
-        <v>0.13333333333333333</v>
+        <v>0.14563106796116504</v>
       </c>
       <c r="V21" s="9">
-        <v>0.0083333333333333332</v>
+        <v>0.012944983818770227</v>
       </c>
       <c r="W21" s="9">
         <v>0</v>
       </c>
       <c r="X21" s="9">
-        <v>0.016666666666666666</v>
+        <v>0.025889967637540454</v>
       </c>
       <c r="Y21" s="9">
-        <v>0</v>
+        <v>0.0032362459546925568</v>
       </c>
       <c r="Z21" s="9">
-        <v>0.0083333333333333332</v>
+        <v>0.0064724919093851136</v>
       </c>
       <c r="AA21" s="9">
-        <v>0.0083333333333333332</v>
+        <v>0.019417475728155338</v>
       </c>
       <c r="AB21" s="9">
         <v>0</v>
@@ -4602,28 +4602,28 @@
         <v>0</v>
       </c>
       <c r="AD21" s="6">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="AE21" s="6">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="AF21" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG21" s="6">
         <v>0</v>
       </c>
       <c r="AH21" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI21" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" s="6">
         <v>2</v>
       </c>
       <c r="AK21" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AL21" s="6">
         <v>0</v>
@@ -4632,10 +4632,10 @@
         <v>0</v>
       </c>
       <c r="AN21" s="9">
-        <v>0.09583333333333334</v>
+        <v>0.093851132686084138</v>
       </c>
       <c r="AO21" s="6">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c t="s" r="AP21" s="4">
         <v>58</v>
@@ -4991,7 +4991,7 @@
         <v>19565</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -5022,61 +5022,61 @@
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="5">
-        <v>36825.940000000002</v>
+        <v>49224.850000000006</v>
       </c>
       <c r="N24" s="6">
-        <v>415</v>
+        <v>555</v>
       </c>
       <c r="O24" s="6">
-        <v>241</v>
+        <v>324</v>
       </c>
       <c r="P24" s="7">
-        <v>2.7320131188118815</v>
+        <v>2.7714285714285714</v>
       </c>
       <c r="Q24" s="8">
-        <v>15.283610373443985</v>
+        <v>15.083127777777777</v>
       </c>
       <c r="R24" s="8">
-        <v>5.9706125603864733</v>
+        <v>5.320023611111111</v>
       </c>
       <c r="S24" s="8">
         <v>8</v>
       </c>
       <c r="T24" s="9">
-        <v>0.57676348547717837</v>
+        <v>0.60802469135802473</v>
       </c>
       <c r="U24" s="9">
-        <v>0.29875518672199169</v>
+        <v>0.26851851851851855</v>
       </c>
       <c r="V24" s="9">
-        <v>0.041493775933609957</v>
+        <v>0.030864197530864196</v>
       </c>
       <c r="W24" s="9">
-        <v>0.0082987551859999998</v>
+        <v>0.006172839506</v>
       </c>
       <c r="X24" s="9">
-        <v>0.070539419087136929</v>
+        <v>0.07098765432098765</v>
       </c>
       <c r="Y24" s="9">
-        <v>0.037344398340248962</v>
+        <v>0.027777777777777776</v>
       </c>
       <c r="Z24" s="9">
-        <v>0.0041493775933609959</v>
+        <v>0.0061728395061728392</v>
       </c>
       <c r="AA24" s="9">
-        <v>0.19502074688796681</v>
+        <v>0.16975308641975309</v>
       </c>
       <c r="AB24" s="9">
-        <v>0.041493775933609957</v>
+        <v>0.040123456790123455</v>
       </c>
       <c r="AC24" s="9">
         <v>0</v>
       </c>
       <c r="AD24" s="6">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="AE24" s="6">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="AF24" s="6">
         <v>10</v>
@@ -5085,19 +5085,19 @@
         <v>2</v>
       </c>
       <c r="AH24" s="6">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AI24" s="6">
         <v>9</v>
       </c>
       <c r="AJ24" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK24" s="6">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="AL24" s="6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AM24" s="6">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>19579</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>51</v>
@@ -5493,61 +5493,61 @@
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="5">
-        <v>26135.610000000001</v>
+        <v>32573.09</v>
       </c>
       <c r="N27" s="6">
-        <v>313</v>
+        <v>379</v>
       </c>
       <c r="O27" s="6">
-        <v>236</v>
+        <v>288</v>
       </c>
       <c r="P27" s="7">
-        <v>6.3113660550458714</v>
+        <v>6.7704412213740452</v>
       </c>
       <c r="Q27" s="8">
-        <v>24.392056595744684</v>
+        <v>23.953600348432055</v>
       </c>
       <c r="R27" s="8">
-        <v>11.201892576419214</v>
+        <v>10.104033451957296</v>
       </c>
       <c r="S27" s="8">
         <v>7</v>
       </c>
       <c r="T27" s="9">
-        <v>0.19148936170212766</v>
+        <v>0.1672473867595819</v>
       </c>
       <c r="U27" s="9">
-        <v>0.1271186440677966</v>
+        <v>0.1076388888888889</v>
       </c>
       <c r="V27" s="9">
-        <v>0.025423728813559324</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="W27" s="9">
-        <v>0.0042372881350000004</v>
+        <v>0.003472222222</v>
       </c>
       <c r="X27" s="9">
-        <v>0.038135593220338986</v>
+        <v>0.03125</v>
       </c>
       <c r="Y27" s="9">
-        <v>0.016949152542372881</v>
+        <v>0.013888888888888888</v>
       </c>
       <c r="Z27" s="9">
-        <v>0.0042372881355932203</v>
+        <v>0.003472222222222222</v>
       </c>
       <c r="AA27" s="9">
-        <v>0.029661016949152543</v>
+        <v>0.024305555555555556</v>
       </c>
       <c r="AB27" s="9">
-        <v>0.012711864406779662</v>
+        <v>0.013888888888888888</v>
       </c>
       <c r="AC27" s="9">
-        <v>0.033898305084745763</v>
+        <v>0.027777777777777776</v>
       </c>
       <c r="AD27" s="6">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AE27" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF27" s="6">
         <v>6</v>
@@ -5568,7 +5568,7 @@
         <v>7</v>
       </c>
       <c r="AL27" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM27" s="6">
         <v>8</v>
@@ -5776,7 +5776,7 @@
         <v>19581</v>
       </c>
       <c r="B29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C29" s="4">
         <v>51</v>
@@ -5807,67 +5807,67 @@
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="5">
-        <v>34691.989999999998</v>
+        <v>52577.989999999998</v>
       </c>
       <c r="N29" s="6">
-        <v>339</v>
+        <v>513</v>
       </c>
       <c r="O29" s="6">
-        <v>269</v>
+        <v>404</v>
       </c>
       <c r="P29" s="7">
-        <v>4.1271750733137829</v>
+        <v>7.687662890625</v>
       </c>
       <c r="Q29" s="8">
-        <v>31.867041198501873</v>
+        <v>34.846093017456354</v>
       </c>
       <c r="R29" s="8">
-        <v>20.423938223938226</v>
+        <v>19.967994858611824</v>
       </c>
       <c r="S29" s="8">
         <v>8</v>
       </c>
       <c r="T29" s="9">
-        <v>0.10861423220973783</v>
+        <v>0.079800498753117205</v>
       </c>
       <c r="U29" s="9">
-        <v>0.13754646840148699</v>
+        <v>0.15841584158415842</v>
       </c>
       <c r="V29" s="9">
-        <v>0.0074349442379182153</v>
+        <v>0.0049504950495049506</v>
       </c>
       <c r="W29" s="9">
-        <v>0.0037174721179999998</v>
+        <v>0.0049504950490000003</v>
       </c>
       <c r="X29" s="9">
-        <v>0.022304832713754646</v>
+        <v>0.014851485148514851</v>
       </c>
       <c r="Y29" s="9">
-        <v>0.011152416356877323</v>
+        <v>0.0074257425742574254</v>
       </c>
       <c r="Z29" s="9">
         <v>0</v>
       </c>
       <c r="AA29" s="9">
-        <v>0.048327137546468404</v>
+        <v>0.042079207920792082</v>
       </c>
       <c r="AB29" s="9">
-        <v>0.011152416356877323</v>
+        <v>0.0074257425742574254</v>
       </c>
       <c r="AC29" s="9">
-        <v>0.059479553903345722</v>
+        <v>0.09405940594059406</v>
       </c>
       <c r="AD29" s="6">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="AE29" s="6">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="AF29" s="6">
         <v>2</v>
       </c>
       <c r="AG29" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH29" s="6">
         <v>6</v>
@@ -5879,13 +5879,13 @@
         <v>0</v>
       </c>
       <c r="AK29" s="6">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AL29" s="6">
         <v>3</v>
       </c>
       <c r="AM29" s="6">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="AN29" s="9">
         <v>0</v>
@@ -6090,7 +6090,7 @@
         <v>19596</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C31" s="4">
         <v>51</v>
@@ -6119,64 +6119,64 @@
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="5">
-        <v>32679.470000000001</v>
+        <v>45471.25</v>
       </c>
       <c r="N31" s="6">
-        <v>375</v>
+        <v>509</v>
       </c>
       <c r="O31" s="6">
-        <v>214</v>
+        <v>295</v>
       </c>
       <c r="P31" s="7">
-        <v>5.5458908587257625</v>
+        <v>6.6975183098591549</v>
       </c>
       <c r="Q31" s="8">
-        <v>23.367448826291078</v>
+        <v>25.373922789115646</v>
       </c>
       <c r="R31" s="8">
-        <v>9.7665876190476197</v>
+        <v>10.087414137931034</v>
       </c>
       <c r="S31" s="8">
         <v>7</v>
       </c>
       <c r="T31" s="9">
-        <v>0.22535211267605634</v>
+        <v>0.18367346938775511</v>
       </c>
       <c r="U31" s="9">
-        <v>0.11682242990654206</v>
+        <v>0.10508474576271186</v>
       </c>
       <c r="V31" s="9">
-        <v>0.037383177570093455</v>
+        <v>0.030508474576271188</v>
       </c>
       <c r="W31" s="9">
-        <v>0.0046728971959999997</v>
+        <v>0.0033898305080000001</v>
       </c>
       <c r="X31" s="9">
-        <v>0.056074766355140186</v>
+        <v>0.040677966101694912</v>
       </c>
       <c r="Y31" s="9">
-        <v>0.014018691588785047</v>
+        <v>0.013559322033898305</v>
       </c>
       <c r="Z31" s="9">
         <v>0</v>
       </c>
       <c r="AA31" s="9">
-        <v>0.014018691588785047</v>
+        <v>0.013559322033898305</v>
       </c>
       <c r="AB31" s="9">
-        <v>0.037383177570093455</v>
+        <v>0.040677966101694912</v>
       </c>
       <c r="AC31" s="9">
         <v>0</v>
       </c>
       <c r="AD31" s="6">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="AE31" s="6">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="AF31" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG31" s="6">
         <v>1</v>
@@ -6185,16 +6185,16 @@
         <v>12</v>
       </c>
       <c r="AI31" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ31" s="6">
         <v>0</v>
       </c>
       <c r="AK31" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL31" s="6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AM31" s="6">
         <v>0</v>
@@ -6712,7 +6712,7 @@
         <v>19601</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C35" s="4">
         <v>51</v>
@@ -6743,85 +6743,85 @@
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="5">
-        <v>30230.720000000001</v>
+        <v>41249.160000000003</v>
       </c>
       <c r="N35" s="6">
-        <v>351</v>
+        <v>474</v>
       </c>
       <c r="O35" s="6">
-        <v>223</v>
+        <v>298</v>
       </c>
       <c r="P35" s="7">
-        <v>2.7497008982035926</v>
+        <v>2.936337142857143</v>
       </c>
       <c r="Q35" s="8">
-        <v>16.137369506726458</v>
+        <v>16.133389597315436</v>
       </c>
       <c r="R35" s="8">
-        <v>5.5355304545454551</v>
+        <v>5.5166093103448279</v>
       </c>
       <c r="S35" s="8">
         <v>8</v>
       </c>
       <c r="T35" s="9">
-        <v>0.50224215246636772</v>
+        <v>0.47651006711409394</v>
       </c>
       <c r="U35" s="9">
-        <v>0.23318385650224216</v>
+        <v>0.26174496644295303</v>
       </c>
       <c r="V35" s="9">
-        <v>0.026905829596412557</v>
+        <v>0.023489932885906041</v>
       </c>
       <c r="W35" s="9">
         <v>0</v>
       </c>
       <c r="X35" s="9">
-        <v>0.049327354260089683</v>
+        <v>0.043624161073825503</v>
       </c>
       <c r="Y35" s="9">
-        <v>0.0044843049327354259</v>
+        <v>0.013422818791946308</v>
       </c>
       <c r="Z35" s="9">
         <v>0</v>
       </c>
       <c r="AA35" s="9">
-        <v>0.06726457399103139</v>
+        <v>0.087248322147651006</v>
       </c>
       <c r="AB35" s="9">
-        <v>0.089686098654708515</v>
+        <v>0.1040268456375839</v>
       </c>
       <c r="AC35" s="9">
-        <v>0.0089686098654708519</v>
+        <v>0.013422818791946308</v>
       </c>
       <c r="AD35" s="6">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AE35" s="6">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="AF35" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG35" s="6">
         <v>0</v>
       </c>
       <c r="AH35" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI35" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ35" s="6">
         <v>0</v>
       </c>
       <c r="AK35" s="6">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="AL35" s="6">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="AM35" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN35" s="9">
         <v>0</v>
@@ -7280,7 +7280,7 @@
         <v>19609</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -7311,70 +7311,70 @@
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="5">
-        <v>28181.110000000001</v>
+        <v>37043.520000000004</v>
       </c>
       <c r="N39" s="6">
-        <v>300</v>
+        <v>398</v>
       </c>
       <c r="O39" s="6">
-        <v>246</v>
+        <v>312</v>
       </c>
       <c r="P39" s="7">
-        <v>5.934539802631579</v>
+        <v>5.792103241895262</v>
       </c>
       <c r="Q39" s="8">
-        <v>29.053455284552843</v>
+        <v>28.093322756410259</v>
       </c>
       <c r="R39" s="8">
-        <v>16.024490204081633</v>
+        <v>15.147856591639872</v>
       </c>
       <c r="S39" s="8">
         <v>7</v>
       </c>
       <c r="T39" s="9">
-        <v>0.12601626016260162</v>
+        <v>0.13782051282051283</v>
       </c>
       <c r="U39" s="9">
-        <v>0.073170731707317069</v>
+        <v>0.089743589743589744</v>
       </c>
       <c r="V39" s="9">
-        <v>0.012195121951219513</v>
+        <v>0.01282051282051282</v>
       </c>
       <c r="W39" s="9">
         <v>0</v>
       </c>
       <c r="X39" s="9">
-        <v>0.008130081300813009</v>
+        <v>0.01282051282051282</v>
       </c>
       <c r="Y39" s="9">
-        <v>0.0040650406504065045</v>
+        <v>0.003205128205128205</v>
       </c>
       <c r="Z39" s="9">
         <v>0</v>
       </c>
       <c r="AA39" s="9">
-        <v>0.008130081300813009</v>
+        <v>0.00641025641025641</v>
       </c>
       <c r="AB39" s="9">
-        <v>0.0040650406504065045</v>
+        <v>0.003205128205128205</v>
       </c>
       <c r="AC39" s="9">
-        <v>0.032520325203252036</v>
+        <v>0.044871794871794872</v>
       </c>
       <c r="AD39" s="6">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AE39" s="6">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AF39" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG39" s="6">
         <v>0</v>
       </c>
       <c r="AH39" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI39" s="6">
         <v>1</v>
@@ -7389,13 +7389,13 @@
         <v>1</v>
       </c>
       <c r="AM39" s="6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AN39" s="9">
-        <v>0.008130081300813009</v>
+        <v>0.0096153846153846159</v>
       </c>
       <c r="AO39" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
@@ -8005,7 +8005,7 @@
         <v>19622</v>
       </c>
       <c r="B44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C44" s="4">
         <v>51</v>
@@ -8036,31 +8036,31 @@
       </c>
       <c r="L44" s="4"/>
       <c r="M44" s="5">
-        <v>30104.360000000001</v>
+        <v>37353.410000000003</v>
       </c>
       <c r="N44" s="6">
-        <v>338</v>
+        <v>429</v>
       </c>
       <c r="O44" s="6">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="P44" s="7">
-        <v>4.8437756172839501</v>
+        <v>4.4859756097560979</v>
       </c>
       <c r="Q44" s="8">
-        <v>14.665333333333335</v>
+        <v>14.624730967741934</v>
       </c>
       <c r="R44" s="8">
-        <v>3.0117021276595741</v>
+        <v>3.0248856164383562</v>
       </c>
       <c r="S44" s="8">
         <v>7</v>
       </c>
       <c r="T44" s="9">
-        <v>0.56666666666666665</v>
+        <v>0.5741935483870968</v>
       </c>
       <c r="U44" s="9">
-        <v>0.10666666666666667</v>
+        <v>0.1032258064516129</v>
       </c>
       <c r="V44" s="9">
         <v>0</v>
@@ -8069,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="X44" s="9">
-        <v>0.013333333333333334</v>
+        <v>0.012903225806451613</v>
       </c>
       <c r="Y44" s="9">
         <v>0</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="AA44" s="9">
-        <v>0.080000000000000002</v>
+        <v>0.077419354838709681</v>
       </c>
       <c r="AB44" s="9">
-        <v>0.013333333333333334</v>
+        <v>0.012903225806451613</v>
       </c>
       <c r="AC44" s="9">
         <v>0</v>
@@ -9666,7 +9666,7 @@
         <v>19649</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9695,79 +9695,79 @@
       </c>
       <c r="L55" s="4"/>
       <c r="M55" s="5">
-        <v>35821.169999999998</v>
+        <v>48331.459999999999</v>
       </c>
       <c r="N55" s="6">
-        <v>422</v>
+        <v>564</v>
       </c>
       <c r="O55" s="6">
-        <v>199</v>
+        <v>259</v>
       </c>
       <c r="P55" s="7">
-        <v>2.7909351219512195</v>
+        <v>2.9328806159420289</v>
       </c>
       <c r="Q55" s="8">
-        <v>15.79673417085427</v>
+        <v>15.573810038610038</v>
       </c>
       <c r="R55" s="8">
-        <v>5.6111400000000007</v>
+        <v>5.2705125506072878</v>
       </c>
       <c r="S55" s="8">
         <v>8</v>
       </c>
       <c r="T55" s="9">
-        <v>0.50251256281407031</v>
+        <v>0.52895752895752901</v>
       </c>
       <c r="U55" s="9">
-        <v>0.22110552763819097</v>
+        <v>0.20849420849420849</v>
       </c>
       <c r="V55" s="9">
-        <v>0.03015075376884422</v>
+        <v>0.027027027027027029</v>
       </c>
       <c r="W55" s="9">
         <v>0</v>
       </c>
       <c r="X55" s="9">
-        <v>0.1306532663316583</v>
+        <v>0.11583011583011583</v>
       </c>
       <c r="Y55" s="9">
-        <v>0.040201005025125629</v>
+        <v>0.034749034749034749</v>
       </c>
       <c r="Z55" s="9">
         <v>0</v>
       </c>
       <c r="AA55" s="9">
-        <v>0.075376884422110546</v>
+        <v>0.088803088803088806</v>
       </c>
       <c r="AB55" s="9">
-        <v>0.035175879396984924</v>
+        <v>0.027027027027027029</v>
       </c>
       <c r="AC55" s="9">
         <v>0</v>
       </c>
       <c r="AD55" s="6">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="AE55" s="6">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="AF55" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG55" s="6">
         <v>0</v>
       </c>
       <c r="AH55" s="6">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI55" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ55" s="6">
         <v>0</v>
       </c>
       <c r="AK55" s="6">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AL55" s="6">
         <v>7</v>
@@ -10228,7 +10228,7 @@
         <v>19657</v>
       </c>
       <c r="B59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C59" s="4">
         <v>51</v>
@@ -10259,61 +10259,61 @@
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="5">
-        <v>29022.25</v>
+        <v>40031.699999999997</v>
       </c>
       <c r="N59" s="6">
-        <v>291</v>
+        <v>403</v>
       </c>
       <c r="O59" s="6">
-        <v>181</v>
+        <v>243</v>
       </c>
       <c r="P59" s="7">
-        <v>9.5109965635738831</v>
+        <v>9.7089359102244384</v>
       </c>
       <c r="Q59" s="8">
-        <v>28.097606077348065</v>
+        <v>29.423113991769547</v>
       </c>
       <c r="R59" s="8">
-        <v>11.808938547486035</v>
+        <v>13.040871369294605</v>
       </c>
       <c r="S59" s="8">
         <v>7</v>
       </c>
       <c r="T59" s="9">
-        <v>0.060773480662983423</v>
+        <v>0.057613168724279837</v>
       </c>
       <c r="U59" s="9">
-        <v>0.25966850828729282</v>
+        <v>0.27160493827160492</v>
       </c>
       <c r="V59" s="9">
-        <v>0.033149171270718231</v>
+        <v>0.024691358024691357</v>
       </c>
       <c r="W59" s="9">
         <v>0</v>
       </c>
       <c r="X59" s="9">
-        <v>0.011049723756906077</v>
+        <v>0.012345679012345678</v>
       </c>
       <c r="Y59" s="9">
-        <v>0.011049723756906077</v>
+        <v>0.00823045267489712</v>
       </c>
       <c r="Z59" s="9">
-        <v>0.011049723756906077</v>
+        <v>0.00823045267489712</v>
       </c>
       <c r="AA59" s="9">
-        <v>0.011049723756906077</v>
+        <v>0.00823045267489712</v>
       </c>
       <c r="AB59" s="9">
-        <v>0.099447513812154692</v>
+        <v>0.098765432098765427</v>
       </c>
       <c r="AC59" s="9">
-        <v>0.11602209944751381</v>
+        <v>0.13991769547325103</v>
       </c>
       <c r="AD59" s="6">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="AE59" s="6">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="AF59" s="6">
         <v>6</v>
@@ -10322,7 +10322,7 @@
         <v>0</v>
       </c>
       <c r="AH59" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI59" s="6">
         <v>2</v>
@@ -10334,10 +10334,10 @@
         <v>2</v>
       </c>
       <c r="AL59" s="6">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AM59" s="6">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AN59" s="9">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>19674</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>51</v>
@@ -10823,31 +10823,31 @@
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="5">
-        <v>33488.919999999998</v>
+        <v>38163.599999999999</v>
       </c>
       <c r="N63" s="6">
-        <v>385</v>
+        <v>440</v>
       </c>
       <c r="O63" s="6">
-        <v>245</v>
+        <v>285</v>
       </c>
       <c r="P63" s="7">
-        <v>5.5033678756476689</v>
+        <v>5.3882801369863014</v>
       </c>
       <c r="Q63" s="8">
-        <v>21.228299591836734</v>
+        <v>21.027368771929826</v>
       </c>
       <c r="R63" s="8">
-        <v>6.1525038626609447</v>
+        <v>6.1687190298507462</v>
       </c>
       <c r="S63" s="8">
         <v>10</v>
       </c>
       <c r="T63" s="9">
-        <v>0.21632653061224491</v>
+        <v>0.22807017543859648</v>
       </c>
       <c r="U63" s="9">
-        <v>0.21224489795918366</v>
+        <v>0.21052631578947367</v>
       </c>
       <c r="V63" s="9">
         <v>0</v>
@@ -10856,28 +10856,28 @@
         <v>0</v>
       </c>
       <c r="X63" s="9">
-        <v>0.036734693877551024</v>
+        <v>0.035087719298245612</v>
       </c>
       <c r="Y63" s="9">
-        <v>0.0040816326530612249</v>
+        <v>0.0035087719298245615</v>
       </c>
       <c r="Z63" s="9">
-        <v>0.0081632653061224497</v>
+        <v>0.0070175438596491229</v>
       </c>
       <c r="AA63" s="9">
-        <v>0.13877551020408163</v>
+        <v>0.14385964912280702</v>
       </c>
       <c r="AB63" s="9">
-        <v>0.012244897959183673</v>
+        <v>0.010526315789473684</v>
       </c>
       <c r="AC63" s="9">
-        <v>0.032653061224489799</v>
+        <v>0.035087719298245612</v>
       </c>
       <c r="AD63" s="6">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="AE63" s="6">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="AF63" s="6">
         <v>0</v>
@@ -10886,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="AH63" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI63" s="6">
         <v>1</v>
@@ -10895,13 +10895,13 @@
         <v>2</v>
       </c>
       <c r="AK63" s="6">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="AL63" s="6">
         <v>3</v>
       </c>
       <c r="AM63" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AN63" s="9">
         <v>0</v>
@@ -12242,7 +12242,7 @@
         <v>19694</v>
       </c>
       <c r="B73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C73" s="4">
         <v>51</v>
@@ -12273,61 +12273,61 @@
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="5">
-        <v>31617.090000000004</v>
+        <v>41442.980000000003</v>
       </c>
       <c r="N73" s="6">
-        <v>336</v>
+        <v>439</v>
       </c>
       <c r="O73" s="6">
-        <v>237</v>
+        <v>317</v>
       </c>
       <c r="P73" s="7">
-        <v>10.901355421686747</v>
+        <v>9.9229885057471261</v>
       </c>
       <c r="Q73" s="8">
-        <v>37.11027327586207</v>
+        <v>34.922062179487178</v>
       </c>
       <c r="R73" s="8">
-        <v>18.909242794759823</v>
+        <v>17.917045129870129</v>
       </c>
       <c r="S73" s="8">
         <v>7</v>
       </c>
       <c r="T73" s="9">
-        <v>0.064655172413793108</v>
+        <v>0.060897435897435896</v>
       </c>
       <c r="U73" s="9">
-        <v>0.13080168776371309</v>
+        <v>0.12618296529968454</v>
       </c>
       <c r="V73" s="9">
-        <v>0.042194092827004218</v>
+        <v>0.031545741324921134</v>
       </c>
       <c r="W73" s="9">
         <v>0</v>
       </c>
       <c r="X73" s="9">
-        <v>0.021097046413502109</v>
+        <v>0.015772870662460567</v>
       </c>
       <c r="Y73" s="9">
-        <v>0.0042194092827004216</v>
+        <v>0.0031545741324921135</v>
       </c>
       <c r="Z73" s="9">
         <v>0</v>
       </c>
       <c r="AA73" s="9">
-        <v>0.012658227848101266</v>
+        <v>0.012618296529968454</v>
       </c>
       <c r="AB73" s="9">
-        <v>0.0084388185654008432</v>
+        <v>0.012618296529968454</v>
       </c>
       <c r="AC73" s="9">
-        <v>0.071729957805907171</v>
+        <v>0.072555205047318619</v>
       </c>
       <c r="AD73" s="6">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="AE73" s="6">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="AF73" s="6">
         <v>10</v>
@@ -12345,13 +12345,13 @@
         <v>0</v>
       </c>
       <c r="AK73" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL73" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM73" s="6">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AN73" s="9">
         <v>0</v>
@@ -13124,7 +13124,7 @@
         <v>19715</v>
       </c>
       <c r="B79" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C79" s="4">
         <v>51</v>
@@ -13155,40 +13155,40 @@
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="5">
-        <v>32750.489999999998</v>
+        <v>43123.209999999999</v>
       </c>
       <c r="N79" s="6">
-        <v>349</v>
+        <v>457</v>
       </c>
       <c r="O79" s="6">
-        <v>221</v>
+        <v>290</v>
       </c>
       <c r="P79" s="7">
-        <v>11.422174928774929</v>
+        <v>11.209154048140045</v>
       </c>
       <c r="Q79" s="8">
-        <v>30.429034841628962</v>
+        <v>30.283678275862069</v>
       </c>
       <c r="R79" s="8">
-        <v>10.066666363636363</v>
+        <v>9.9784142361111119</v>
       </c>
       <c r="S79" s="8">
         <v>9</v>
       </c>
       <c r="T79" s="9">
-        <v>0.049773755656108594</v>
+        <v>0.041379310344827586</v>
       </c>
       <c r="U79" s="9">
-        <v>0.095022624434389136</v>
+        <v>0.14827586206896551</v>
       </c>
       <c r="V79" s="9">
-        <v>0</v>
+        <v>0.0034482758620689655</v>
       </c>
       <c r="W79" s="9">
         <v>0</v>
       </c>
       <c r="X79" s="9">
-        <v>0.031674208144796379</v>
+        <v>0.024137931034482758</v>
       </c>
       <c r="Y79" s="9">
         <v>0</v>
@@ -13197,22 +13197,22 @@
         <v>0</v>
       </c>
       <c r="AA79" s="9">
-        <v>0.0045248868778280547</v>
+        <v>0.010344827586206896</v>
       </c>
       <c r="AB79" s="9">
-        <v>0.063348416289592757</v>
+        <v>0.11379310344827587</v>
       </c>
       <c r="AC79" s="9">
         <v>0</v>
       </c>
       <c r="AD79" s="6">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AE79" s="6">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="AF79" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG79" s="6">
         <v>0</v>
@@ -13227,10 +13227,10 @@
         <v>0</v>
       </c>
       <c r="AK79" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL79" s="6">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="AM79" s="6">
         <v>0</v>
@@ -14417,7 +14417,7 @@
         <v>19730</v>
       </c>
       <c r="B88" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C88" s="4">
         <v>51</v>
@@ -14446,40 +14446,40 @@
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="5">
-        <v>43526.07</v>
+        <v>56224</v>
       </c>
       <c r="N88" s="6">
-        <v>442</v>
+        <v>580</v>
       </c>
       <c r="O88" s="6">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="P88" s="7">
-        <v>4.8321029082774043</v>
+        <v>4.8923623509369678</v>
       </c>
       <c r="Q88" s="8">
-        <v>23.727558267716535</v>
+        <v>23.244443790849672</v>
       </c>
       <c r="R88" s="8">
-        <v>10.552887401574802</v>
+        <v>10.149564705882353</v>
       </c>
       <c r="S88" s="8">
         <v>8</v>
       </c>
       <c r="T88" s="9">
-        <v>0.16535433070866143</v>
+        <v>0.1437908496732026</v>
       </c>
       <c r="U88" s="9">
-        <v>0.56692913385826771</v>
+        <v>0.5163398692810458</v>
       </c>
       <c r="V88" s="9">
-        <v>0.2125984251968504</v>
+        <v>0.17647058823529413</v>
       </c>
       <c r="W88" s="9">
         <v>0</v>
       </c>
       <c r="X88" s="9">
-        <v>0.031496062992125984</v>
+        <v>0.026143790849673203</v>
       </c>
       <c r="Y88" s="9">
         <v>0</v>
@@ -14488,19 +14488,19 @@
         <v>0</v>
       </c>
       <c r="AA88" s="9">
-        <v>0.007874015748031496</v>
+        <v>0.0065359477124183009</v>
       </c>
       <c r="AB88" s="9">
-        <v>0.11023622047244094</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="AC88" s="9">
-        <v>0.29921259842519687</v>
+        <v>0.27450980392156865</v>
       </c>
       <c r="AD88" s="6">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="AE88" s="6">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="AF88" s="6">
         <v>27</v>
@@ -14521,10 +14521,10 @@
         <v>1</v>
       </c>
       <c r="AL88" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AM88" s="6">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AN88" s="9">
         <v>0</v>
@@ -15706,7 +15706,7 @@
         <v>19749</v>
       </c>
       <c r="B97" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C97" s="4">
         <v>51</v>
@@ -15735,70 +15735,70 @@
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="5">
-        <v>19428.670000000002</v>
+        <v>24519.530000000002</v>
       </c>
       <c r="N97" s="6">
-        <v>199</v>
+        <v>249</v>
       </c>
       <c r="O97" s="6">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="P97" s="7">
-        <v>4.1761908163265309</v>
+        <v>4.6620221311475412</v>
       </c>
       <c r="Q97" s="8">
-        <v>21.76997272727273</v>
+        <v>23.358766233766232</v>
       </c>
       <c r="R97" s="8">
-        <v>9.8527783333333332</v>
+        <v>11.055229411764707</v>
       </c>
       <c r="S97" s="8">
         <v>8</v>
       </c>
       <c r="T97" s="9">
-        <v>0.18181818181818182</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="U97" s="9">
-        <v>0.10743801652892562</v>
+        <v>0.11688311688311688</v>
       </c>
       <c r="V97" s="9">
-        <v>0.033057851239669422</v>
+        <v>0.03896103896103896</v>
       </c>
       <c r="W97" s="9">
-        <v>0</v>
+        <v>0.0064935064929999998</v>
       </c>
       <c r="X97" s="9">
-        <v>0.041322314049586778</v>
+        <v>0.045454545454545456</v>
       </c>
       <c r="Y97" s="9">
-        <v>0.0082644628099173556</v>
+        <v>0.0064935064935064939</v>
       </c>
       <c r="Z97" s="9">
-        <v>0.0082644628099173556</v>
+        <v>0.0064935064935064939</v>
       </c>
       <c r="AA97" s="9">
-        <v>0.024793388429752067</v>
+        <v>0.01948051948051948</v>
       </c>
       <c r="AB97" s="9">
         <v>0</v>
       </c>
       <c r="AC97" s="9">
-        <v>0.016528925619834711</v>
+        <v>0.025974025974025976</v>
       </c>
       <c r="AD97" s="6">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AE97" s="6">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AF97" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG97" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH97" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI97" s="6">
         <v>1</v>
@@ -15813,7 +15813,7 @@
         <v>0</v>
       </c>
       <c r="AM97" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN97" s="9">
         <v>0</v>
@@ -18214,7 +18214,7 @@
         <v>19785</v>
       </c>
       <c r="B113" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C113" s="4">
         <v>51</v>
@@ -18245,64 +18245,64 @@
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="5">
-        <v>22218.32</v>
+        <v>30560.720000000001</v>
       </c>
       <c r="N113" s="6">
-        <v>209</v>
+        <v>286</v>
       </c>
       <c r="O113" s="6">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="P113" s="7">
-        <v>5.9586956521739136</v>
+        <v>6.0458187279151945</v>
       </c>
       <c r="Q113" s="8">
-        <v>18.217433333333332</v>
+        <v>18.886835294117645</v>
       </c>
       <c r="R113" s="8">
-        <v>6.5660341772151893</v>
+        <v>7.3280373831775707</v>
       </c>
       <c r="S113" s="8">
         <v>7</v>
       </c>
       <c r="T113" s="9">
-        <v>0.45977011494252873</v>
+        <v>0.46218487394957986</v>
       </c>
       <c r="U113" s="9">
-        <v>0.40229885057471265</v>
+        <v>0.40336134453781514</v>
       </c>
       <c r="V113" s="9">
-        <v>0.045977011494252873</v>
+        <v>0.042016806722689079</v>
       </c>
       <c r="W113" s="9">
-        <v>0.011494252873</v>
+        <v>0.0084033613440000002</v>
       </c>
       <c r="X113" s="9">
-        <v>0.034482758620689655</v>
+        <v>0.025210084033613446</v>
       </c>
       <c r="Y113" s="9">
-        <v>0.011494252873563218</v>
+        <v>0.0084033613445378148</v>
       </c>
       <c r="Z113" s="9">
         <v>0</v>
       </c>
       <c r="AA113" s="9">
-        <v>0.2988505747126437</v>
+        <v>0.31932773109243695</v>
       </c>
       <c r="AB113" s="9">
         <v>0</v>
       </c>
       <c r="AC113" s="9">
-        <v>0.068965517241379309</v>
+        <v>0.050420168067226892</v>
       </c>
       <c r="AD113" s="6">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="AE113" s="6">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="AF113" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG113" s="6">
         <v>1</v>
@@ -18317,7 +18317,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="6">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AL113" s="6">
         <v>0</v>
@@ -19972,7 +19972,7 @@
         <v>19842</v>
       </c>
       <c r="B125" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C125" s="4">
         <v>51</v>
@@ -20003,85 +20003,85 @@
       </c>
       <c r="L125" s="4"/>
       <c r="M125" s="5">
-        <v>53927.970000000008</v>
+        <v>67539.160000000003</v>
       </c>
       <c r="N125" s="6">
-        <v>524</v>
+        <v>653</v>
       </c>
       <c r="O125" s="6">
-        <v>337</v>
+        <v>436</v>
       </c>
       <c r="P125" s="7">
-        <v>5.3954909819639276</v>
+        <v>5.7604299363057327</v>
       </c>
       <c r="Q125" s="8">
-        <v>23.233283976261127</v>
+        <v>24.526873165137616</v>
       </c>
       <c r="R125" s="8">
-        <v>10.813931578947368</v>
+        <v>12.241972127139364</v>
       </c>
       <c r="S125" s="8">
         <v>8</v>
       </c>
       <c r="T125" s="9">
-        <v>0.083086053412462904</v>
+        <v>0.094036697247706427</v>
       </c>
       <c r="U125" s="9">
-        <v>0.13056379821958458</v>
+        <v>0.13990825688073394</v>
       </c>
       <c r="V125" s="9">
-        <v>0.053412462908011868</v>
+        <v>0.052752293577981654</v>
       </c>
       <c r="W125" s="9">
-        <v>0.017804154302000001</v>
+        <v>0.043577981650999999</v>
       </c>
       <c r="X125" s="9">
-        <v>0.023738872403560832</v>
+        <v>0.020642201834862386</v>
       </c>
       <c r="Y125" s="9">
-        <v>0.035608308605341248</v>
+        <v>0.057339449541284407</v>
       </c>
       <c r="Z125" s="9">
-        <v>0.002967359050445104</v>
+        <v>0.0022935779816513763</v>
       </c>
       <c r="AA125" s="9">
-        <v>0.041543026706231452</v>
+        <v>0.061926605504587159</v>
       </c>
       <c r="AB125" s="9">
-        <v>0.02967359050445104</v>
+        <v>0.022935779816513763</v>
       </c>
       <c r="AC125" s="9">
-        <v>0</v>
+        <v>0.0045871559633027525</v>
       </c>
       <c r="AD125" s="6">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="AE125" s="6">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="AF125" s="6">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AG125" s="6">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AH125" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI125" s="6">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="AJ125" s="6">
         <v>1</v>
       </c>
       <c r="AK125" s="6">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AL125" s="6">
         <v>10</v>
       </c>
       <c r="AM125" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN125" s="9">
         <v>0</v>
@@ -20166,7 +20166,7 @@
         <v>263</v>
       </c>
       <c r="O126" s="6">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="P126" s="7">
         <v>3.6984674329501912</v>
@@ -20184,46 +20184,46 @@
         <v>0.27777777777777779</v>
       </c>
       <c r="U126" s="9">
-        <v>0.30392156862745096</v>
+        <v>0.31944444444444442</v>
       </c>
       <c r="V126" s="9">
-        <v>0.078431372549019607</v>
+        <v>0.0625</v>
       </c>
       <c r="W126" s="9">
         <v>0</v>
       </c>
       <c r="X126" s="9">
-        <v>0.15686274509803921</v>
+        <v>0.125</v>
       </c>
       <c r="Y126" s="9">
-        <v>0.019607843137254902</v>
+        <v>0.013888888888888888</v>
       </c>
       <c r="Z126" s="9">
         <v>0</v>
       </c>
       <c r="AA126" s="9">
-        <v>0.11764705882352941</v>
+        <v>0.097222222222222224</v>
       </c>
       <c r="AB126" s="9">
-        <v>0</v>
+        <v>0.0069444444444444441</v>
       </c>
       <c r="AC126" s="9">
-        <v>0.039215686274509803</v>
+        <v>0.083333333333333329</v>
       </c>
       <c r="AD126" s="6">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="AE126" s="6">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="AF126" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG126" s="6">
         <v>0</v>
       </c>
       <c r="AH126" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI126" s="6">
         <v>2</v>
@@ -20232,19 +20232,19 @@
         <v>0</v>
       </c>
       <c r="AK126" s="6">
+        <v>14</v>
+      </c>
+      <c r="AL126" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM126" s="6">
         <v>12</v>
       </c>
-      <c r="AL126" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM126" s="6">
-        <v>4</v>
-      </c>
       <c r="AN126" s="9">
-        <v>0.019607843137254902</v>
+        <v>0.020833333333333332</v>
       </c>
       <c r="AO126" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c t="s" r="AP126" s="4">
         <v>58</v>
@@ -20443,7 +20443,7 @@
         <v>19859</v>
       </c>
       <c r="B128" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C128" s="4">
         <v>51</v>
@@ -20474,61 +20474,61 @@
       </c>
       <c r="L128" s="4"/>
       <c r="M128" s="5">
-        <v>23495.799999999999</v>
+        <v>29937.16</v>
       </c>
       <c r="N128" s="6">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="O128" s="6">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="P128" s="7">
-        <v>7.7475510204081637</v>
+        <v>8.5786407766990305</v>
       </c>
       <c r="Q128" s="8">
-        <v>21.834020103092783</v>
+        <v>22.90304837398374</v>
       </c>
       <c r="R128" s="8">
-        <v>6.6647762886597937</v>
+        <v>6.8448508130081303</v>
       </c>
       <c r="S128" s="8">
         <v>7</v>
       </c>
       <c r="T128" s="9">
-        <v>0.27835051546391754</v>
+        <v>0.23577235772357724</v>
       </c>
       <c r="U128" s="9">
-        <v>0.041237113402061855</v>
+        <v>0.036585365853658534</v>
       </c>
       <c r="V128" s="9">
-        <v>0.0051546391752577319</v>
+        <v>0.0040650406504065045</v>
       </c>
       <c r="W128" s="9">
         <v>0</v>
       </c>
       <c r="X128" s="9">
-        <v>0.015463917525773196</v>
+        <v>0.012195121951219513</v>
       </c>
       <c r="Y128" s="9">
         <v>0</v>
       </c>
       <c r="Z128" s="9">
-        <v>0.0051546391752577319</v>
+        <v>0.008130081300813009</v>
       </c>
       <c r="AA128" s="9">
         <v>0</v>
       </c>
       <c r="AB128" s="9">
-        <v>0.0051546391752577319</v>
+        <v>0.0040650406504065045</v>
       </c>
       <c r="AC128" s="9">
-        <v>0.010309278350515464</v>
+        <v>0.008130081300813009</v>
       </c>
       <c r="AD128" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE128" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF128" s="6">
         <v>1</v>
@@ -20543,7 +20543,7 @@
         <v>0</v>
       </c>
       <c r="AJ128" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK128" s="6">
         <v>0</v>
@@ -21633,7 +21633,7 @@
         <v>19881</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>51</v>
@@ -21664,70 +21664,70 @@
       </c>
       <c r="L136" s="4"/>
       <c r="M136" s="5">
-        <v>61251.619999999995</v>
+        <v>77036.239999999991</v>
       </c>
       <c r="N136" s="6">
-        <v>541</v>
+        <v>681</v>
       </c>
       <c r="O136" s="6">
-        <v>402</v>
+        <v>499</v>
       </c>
       <c r="P136" s="7">
-        <v>3.2238355716878404</v>
+        <v>3.2621147398843933</v>
       </c>
       <c r="Q136" s="8">
-        <v>20.931467910447761</v>
+        <v>20.250902004008015</v>
       </c>
       <c r="R136" s="8">
-        <v>11.91222205128205</v>
+        <v>11.123887679671459</v>
       </c>
       <c r="S136" s="8">
         <v>6.2999999999999998</v>
       </c>
       <c r="T136" s="9">
-        <v>0.29104477611940299</v>
+        <v>0.30060120240480964</v>
       </c>
       <c r="U136" s="9">
-        <v>0.092039800995024873</v>
+        <v>0.08617234468937876</v>
       </c>
       <c r="V136" s="9">
-        <v>0.047263681592039801</v>
+        <v>0.044088176352705413</v>
       </c>
       <c r="W136" s="9">
-        <v>0.0024875621890000001</v>
+        <v>0.0020040080160000002</v>
       </c>
       <c r="X136" s="9">
-        <v>0.014925373134328358</v>
+        <v>0.018036072144288578</v>
       </c>
       <c r="Y136" s="9">
-        <v>0.014925373134328358</v>
+        <v>0.012024048096192385</v>
       </c>
       <c r="Z136" s="9">
         <v>0</v>
       </c>
       <c r="AA136" s="9">
-        <v>0.03482587064676617</v>
+        <v>0.028056112224448898</v>
       </c>
       <c r="AB136" s="9">
-        <v>0.007462686567164179</v>
+        <v>0.0060120240480961923</v>
       </c>
       <c r="AC136" s="9">
-        <v>0.0099502487562189053</v>
+        <v>0.0080160320641282558</v>
       </c>
       <c r="AD136" s="6">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="AE136" s="6">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AF136" s="6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AG136" s="6">
         <v>1</v>
       </c>
       <c r="AH136" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AI136" s="6">
         <v>6</v>
@@ -21947,7 +21947,7 @@
         <v>19884</v>
       </c>
       <c r="B138" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C138" s="4">
         <v>51</v>
@@ -21978,31 +21978,31 @@
       </c>
       <c r="L138" s="4"/>
       <c r="M138" s="5">
-        <v>21610.779999999999</v>
+        <v>27885.639999999999</v>
       </c>
       <c r="N138" s="6">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="O138" s="6">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="P138" s="7">
-        <v>8.5979508196721319</v>
+        <v>8.3065477272727275</v>
       </c>
       <c r="Q138" s="8">
-        <v>22.550097093023258</v>
+        <v>22.694618834080718</v>
       </c>
       <c r="R138" s="8">
-        <v>7.2729166666666663</v>
+        <v>7.9418848167539275</v>
       </c>
       <c r="S138" s="8">
         <v>7</v>
       </c>
       <c r="T138" s="9">
-        <v>0.26744186046511625</v>
+        <v>0.22421524663677131</v>
       </c>
       <c r="U138" s="9">
-        <v>0.20348837209302326</v>
+        <v>0.17488789237668162</v>
       </c>
       <c r="V138" s="9">
         <v>0</v>
@@ -22011,28 +22011,28 @@
         <v>0</v>
       </c>
       <c r="X138" s="9">
-        <v>0.011627906976744186</v>
+        <v>0.0089686098654708519</v>
       </c>
       <c r="Y138" s="9">
-        <v>0.0058139534883720929</v>
+        <v>0.0089686098654708519</v>
       </c>
       <c r="Z138" s="9">
         <v>0</v>
       </c>
       <c r="AA138" s="9">
-        <v>0.18023255813953487</v>
+        <v>0.15695067264573992</v>
       </c>
       <c r="AB138" s="9">
-        <v>0.017441860465116279</v>
+        <v>0.013452914798206279</v>
       </c>
       <c r="AC138" s="9">
-        <v>0.011627906976744186</v>
+        <v>0.0089686098654708519</v>
       </c>
       <c r="AD138" s="6">
+        <v>44</v>
+      </c>
+      <c r="AE138" s="6">
         <v>39</v>
-      </c>
-      <c r="AE138" s="6">
-        <v>35</v>
       </c>
       <c r="AF138" s="6">
         <v>0</v>
@@ -22044,13 +22044,13 @@
         <v>2</v>
       </c>
       <c r="AI138" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ138" s="6">
         <v>0</v>
       </c>
       <c r="AK138" s="6">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AL138" s="6">
         <v>3</v>
@@ -23176,7 +23176,7 @@
         <v>162</v>
       </c>
       <c r="O146" s="6">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="P146" s="7">
         <v>5.5688360946745563</v>
@@ -23194,7 +23194,7 @@
         <v>0.21428571428571427</v>
       </c>
       <c r="U146" s="9">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="V146" s="9">
         <v>0</v>
@@ -23203,7 +23203,7 @@
         <v>0</v>
       </c>
       <c r="X146" s="9">
-        <v>0.125</v>
+        <v>0.047619047619047616</v>
       </c>
       <c r="Y146" s="9">
         <v>0</v>
@@ -23212,19 +23212,19 @@
         <v>0</v>
       </c>
       <c r="AA146" s="9">
-        <v>0</v>
+        <v>0.071428571428571425</v>
       </c>
       <c r="AB146" s="9">
-        <v>0</v>
+        <v>0.071428571428571425</v>
       </c>
       <c r="AC146" s="9">
-        <v>0.5</v>
+        <v>0.47619047619047616</v>
       </c>
       <c r="AD146" s="6">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="AE146" s="6">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="AF146" s="6">
         <v>0</v>
@@ -23233,7 +23233,7 @@
         <v>0</v>
       </c>
       <c r="AH146" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI146" s="6">
         <v>0</v>
@@ -23242,13 +23242,13 @@
         <v>0</v>
       </c>
       <c r="AK146" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL146" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AM146" s="6">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AN146" s="9">
         <v>0</v>
@@ -23296,7 +23296,7 @@
         <v>19910</v>
       </c>
       <c r="B147" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C147" s="4">
         <v>51</v>
@@ -23327,40 +23327,40 @@
       </c>
       <c r="L147" s="4"/>
       <c r="M147" s="5">
-        <v>19128.139999999999</v>
+        <v>25473.889999999999</v>
       </c>
       <c r="N147" s="6">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="O147" s="6">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="P147" s="7">
-        <v>5.638162149532711</v>
+        <v>5.1200485507246372</v>
       </c>
       <c r="Q147" s="8">
-        <v>17.107300826446281</v>
+        <v>15.534839354838709</v>
       </c>
       <c r="R147" s="8">
-        <v>11.236857692307693</v>
+        <v>9.7521852459016394</v>
       </c>
       <c r="S147" s="8">
         <v>8</v>
       </c>
       <c r="T147" s="9">
-        <v>0.69421487603305787</v>
+        <v>0.74193548387096775</v>
       </c>
       <c r="U147" s="9">
-        <v>0.75409836065573765</v>
+        <v>0.76282051282051277</v>
       </c>
       <c r="V147" s="9">
-        <v>0.016393442622950821</v>
+        <v>0.01282051282051282</v>
       </c>
       <c r="W147" s="9">
         <v>0</v>
       </c>
       <c r="X147" s="9">
-        <v>0.016393442622950821</v>
+        <v>0.02564102564102564</v>
       </c>
       <c r="Y147" s="9">
         <v>0</v>
@@ -23369,19 +23369,19 @@
         <v>0</v>
       </c>
       <c r="AA147" s="9">
-        <v>0.70491803278688525</v>
+        <v>0.72435897435897434</v>
       </c>
       <c r="AB147" s="9">
-        <v>0.024590163934426229</v>
+        <v>0.019230769230769232</v>
       </c>
       <c r="AC147" s="9">
-        <v>0.049180327868852458</v>
+        <v>0.05128205128205128</v>
       </c>
       <c r="AD147" s="6">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="AE147" s="6">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="AF147" s="6">
         <v>2</v>
@@ -23390,7 +23390,7 @@
         <v>0</v>
       </c>
       <c r="AH147" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI147" s="6">
         <v>0</v>
@@ -23399,13 +23399,13 @@
         <v>0</v>
       </c>
       <c r="AK147" s="6">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="AL147" s="6">
         <v>3</v>
       </c>
       <c r="AM147" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN147" s="9">
         <v>0</v>
@@ -24180,7 +24180,7 @@
         <v>19927</v>
       </c>
       <c r="B153" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C153" s="4">
         <v>51</v>
@@ -24211,40 +24211,40 @@
       </c>
       <c r="L153" s="4"/>
       <c r="M153" s="5">
-        <v>8726.6599999999999</v>
+        <v>10822.639999999999</v>
       </c>
       <c r="N153" s="6">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="O153" s="6">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="P153" s="7">
-        <v>9.6891891891891895</v>
+        <v>9.1664266187050352</v>
       </c>
       <c r="Q153" s="8">
-        <v>29.206816666666665</v>
+        <v>27.089009890109892</v>
       </c>
       <c r="R153" s="8">
-        <v>13.117928787878789</v>
+        <v>11.812222222222221</v>
       </c>
       <c r="S153" s="8">
         <v>7</v>
       </c>
       <c r="T153" s="9">
-        <v>0.13636363636363635</v>
+        <v>0.17582417582417584</v>
       </c>
       <c r="U153" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.19780219780219779</v>
       </c>
       <c r="V153" s="9">
-        <v>0.060606060606060608</v>
+        <v>0.087912087912087919</v>
       </c>
       <c r="W153" s="9">
         <v>0</v>
       </c>
       <c r="X153" s="9">
-        <v>0.045454545454545456</v>
+        <v>0.043956043956043959</v>
       </c>
       <c r="Y153" s="9">
         <v>0</v>
@@ -24253,40 +24253,40 @@
         <v>0</v>
       </c>
       <c r="AA153" s="9">
-        <v>0.015151515151515152</v>
+        <v>0.032967032967032968</v>
       </c>
       <c r="AB153" s="9">
-        <v>0.015151515151515152</v>
+        <v>0.02197802197802198</v>
       </c>
       <c r="AC153" s="9">
-        <v>0.030303030303030304</v>
+        <v>0.02197802197802198</v>
       </c>
       <c r="AD153" s="6">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AE153" s="6">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AF153" s="6">
+        <v>8</v>
+      </c>
+      <c r="AG153" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH153" s="6">
         <v>4</v>
       </c>
-      <c r="AG153" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH153" s="6">
+      <c r="AI153" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ153" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK153" s="6">
         <v>3</v>
       </c>
-      <c r="AI153" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ153" s="6">
-        <v>0</v>
-      </c>
-      <c r="AK153" s="6">
-        <v>1</v>
-      </c>
       <c r="AL153" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM153" s="6">
         <v>2</v>
@@ -24494,7 +24494,7 @@
         <v>19930</v>
       </c>
       <c r="B155" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C155" s="4">
         <v>51</v>
@@ -24525,61 +24525,61 @@
       </c>
       <c r="L155" s="4"/>
       <c r="M155" s="5">
-        <v>21979.389999999999</v>
+        <v>29465.239999999998</v>
       </c>
       <c r="N155" s="6">
-        <v>325</v>
+        <v>442</v>
       </c>
       <c r="O155" s="6">
-        <v>274</v>
+        <v>387</v>
       </c>
       <c r="P155" s="7">
-        <v>4.7077199386503068</v>
+        <v>4.692851918735891</v>
       </c>
       <c r="Q155" s="8">
-        <v>23.090571532846717</v>
+        <v>22.819121188630493</v>
       </c>
       <c r="R155" s="8">
-        <v>11.687856505576207</v>
+        <v>11.426290551181102</v>
       </c>
       <c r="S155" s="8">
         <v>7</v>
       </c>
       <c r="T155" s="9">
-        <v>0.13868613138686131</v>
+        <v>0.12403100775193798</v>
       </c>
       <c r="U155" s="9">
-        <v>0.46715328467153283</v>
+        <v>0.40310077519379844</v>
       </c>
       <c r="V155" s="9">
-        <v>0.01824817518248175</v>
+        <v>0.012919896640826873</v>
       </c>
       <c r="W155" s="9">
         <v>0</v>
       </c>
       <c r="X155" s="9">
-        <v>0.01824817518248175</v>
+        <v>0.023255813953488372</v>
       </c>
       <c r="Y155" s="9">
-        <v>0.010948905109489052</v>
+        <v>0.0077519379844961239</v>
       </c>
       <c r="Z155" s="9">
-        <v>0.0036496350364963502</v>
+        <v>0.0025839793281653748</v>
       </c>
       <c r="AA155" s="9">
-        <v>0.021897810218978103</v>
+        <v>0.018087855297157621</v>
       </c>
       <c r="AB155" s="9">
-        <v>0.01824817518248175</v>
+        <v>0.012919896640826873</v>
       </c>
       <c r="AC155" s="9">
-        <v>0.41605839416058393</v>
+        <v>0.35658914728682173</v>
       </c>
       <c r="AD155" s="6">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="AE155" s="6">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="AF155" s="6">
         <v>5</v>
@@ -24588,7 +24588,7 @@
         <v>0</v>
       </c>
       <c r="AH155" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AI155" s="6">
         <v>3</v>
@@ -24597,13 +24597,13 @@
         <v>1</v>
       </c>
       <c r="AK155" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL155" s="6">
         <v>5</v>
       </c>
       <c r="AM155" s="6">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="AN155" s="9">
         <v>0</v>
@@ -24651,7 +24651,7 @@
         <v>19931</v>
       </c>
       <c r="B156" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>51</v>
@@ -24682,82 +24682,82 @@
       </c>
       <c r="L156" s="4"/>
       <c r="M156" s="5">
-        <v>24728.470000000001</v>
+        <v>35963.740000000005</v>
       </c>
       <c r="N156" s="6">
-        <v>258</v>
+        <v>377</v>
       </c>
       <c r="O156" s="6">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="P156" s="7">
-        <v>4.7310936758893281</v>
+        <v>4.6928636856368566</v>
       </c>
       <c r="Q156" s="8">
-        <v>16.373393577981652</v>
+        <v>16.182687741935485</v>
       </c>
       <c r="R156" s="8">
-        <v>4.6699999999999999</v>
+        <v>4.5500000000000007</v>
       </c>
       <c r="S156" s="8">
         <v>7</v>
       </c>
       <c r="T156" s="9">
-        <v>0.51376146788990829</v>
+        <v>0.49677419354838709</v>
       </c>
       <c r="U156" s="9">
-        <v>0.11009174311926606</v>
+        <v>0.13548387096774195</v>
       </c>
       <c r="V156" s="9">
-        <v>0.0091743119266055051</v>
+        <v>0.01935483870967742</v>
       </c>
       <c r="W156" s="9">
         <v>0</v>
       </c>
       <c r="X156" s="9">
-        <v>0.01834862385321101</v>
+        <v>0.03870967741935484</v>
       </c>
       <c r="Y156" s="9">
-        <v>0.0091743119266055051</v>
+        <v>0.012903225806451613</v>
       </c>
       <c r="Z156" s="9">
-        <v>0.0091743119266055051</v>
+        <v>0.0064516129032258064</v>
       </c>
       <c r="AA156" s="9">
-        <v>0.082568807339449546</v>
+        <v>0.090322580645161285</v>
       </c>
       <c r="AB156" s="9">
-        <v>0</v>
+        <v>0.025806451612903226</v>
       </c>
       <c r="AC156" s="9">
         <v>0</v>
       </c>
       <c r="AD156" s="6">
+        <v>30</v>
+      </c>
+      <c r="AE156" s="6">
+        <v>21</v>
+      </c>
+      <c r="AF156" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG156" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH156" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI156" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ156" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK156" s="6">
         <v>14</v>
       </c>
-      <c r="AE156" s="6">
-        <v>12</v>
-      </c>
-      <c r="AF156" s="6">
-        <v>1</v>
-      </c>
-      <c r="AG156" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH156" s="6">
-        <v>2</v>
-      </c>
-      <c r="AI156" s="6">
-        <v>1</v>
-      </c>
-      <c r="AJ156" s="6">
-        <v>1</v>
-      </c>
-      <c r="AK156" s="6">
-        <v>9</v>
-      </c>
       <c r="AL156" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM156" s="6">
         <v>0</v>
@@ -25277,7 +25277,7 @@
         <v>19943</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C160" s="4">
         <v>51</v>
@@ -25308,40 +25308,40 @@
       </c>
       <c r="L160" s="4"/>
       <c r="M160" s="5">
-        <v>14824.26</v>
+        <v>20611.77</v>
       </c>
       <c r="N160" s="6">
-        <v>166</v>
+        <v>230</v>
       </c>
       <c r="O160" s="6">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="P160" s="7">
-        <v>8.6490734567901235</v>
+        <v>9.3661455357142849</v>
       </c>
       <c r="Q160" s="8">
-        <v>29.436600980392157</v>
+        <v>27.766296296296296</v>
       </c>
       <c r="R160" s="8">
-        <v>15.161</v>
+        <v>13.373737121212121</v>
       </c>
       <c r="S160" s="8">
         <v>7</v>
       </c>
       <c r="T160" s="9">
-        <v>0.17647058823529413</v>
+        <v>0.18518518518518517</v>
       </c>
       <c r="U160" s="9">
-        <v>0.22549019607843138</v>
+        <v>0.23703703703703705</v>
       </c>
       <c r="V160" s="9">
-        <v>0.058823529411764705</v>
+        <v>0.066666666666666666</v>
       </c>
       <c r="W160" s="9">
         <v>0</v>
       </c>
       <c r="X160" s="9">
-        <v>0.058823529411764705</v>
+        <v>0.059259259259259262</v>
       </c>
       <c r="Y160" s="9">
         <v>0</v>
@@ -25350,28 +25350,28 @@
         <v>0</v>
       </c>
       <c r="AA160" s="9">
-        <v>0.029411764705882353</v>
+        <v>0.029629629629629631</v>
       </c>
       <c r="AB160" s="9">
-        <v>0.019607843137254902</v>
+        <v>0.029629629629629631</v>
       </c>
       <c r="AC160" s="9">
-        <v>0.098039215686274508</v>
+        <v>0.088888888888888892</v>
       </c>
       <c r="AD160" s="6">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="AE160" s="6">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AF160" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG160" s="6">
         <v>0</v>
       </c>
       <c r="AH160" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI160" s="6">
         <v>0</v>
@@ -25380,13 +25380,13 @@
         <v>0</v>
       </c>
       <c r="AK160" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL160" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM160" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AN160" s="9">
         <v>0</v>
@@ -26062,7 +26062,7 @@
         <v>19951</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26093,61 +26093,61 @@
       </c>
       <c r="L165" s="4"/>
       <c r="M165" s="5">
-        <v>22616.130000000001</v>
+        <v>32516.190000000002</v>
       </c>
       <c r="N165" s="6">
-        <v>228</v>
+        <v>330</v>
       </c>
       <c r="O165" s="6">
-        <v>125</v>
+        <v>179</v>
       </c>
       <c r="P165" s="7">
-        <v>4.7817777777777781</v>
+        <v>5.4757436923076925</v>
       </c>
       <c r="Q165" s="8">
-        <v>16.990666399999999</v>
+        <v>16.947486033519553</v>
       </c>
       <c r="R165" s="8">
-        <v>5.1151756097560979</v>
+        <v>4.5796397727272726</v>
       </c>
       <c r="S165" s="8">
         <v>7</v>
       </c>
       <c r="T165" s="9">
-        <v>0.504</v>
+        <v>0.49162011173184356</v>
       </c>
       <c r="U165" s="9">
-        <v>0.064000000000000001</v>
+        <v>0.089385474860335198</v>
       </c>
       <c r="V165" s="9">
-        <v>0.0080000000000000002</v>
+        <v>0.0055865921787709499</v>
       </c>
       <c r="W165" s="9">
         <v>0</v>
       </c>
       <c r="X165" s="9">
-        <v>0.0080000000000000002</v>
+        <v>0.0111731843575419</v>
       </c>
       <c r="Y165" s="9">
         <v>0</v>
       </c>
       <c r="Z165" s="9">
-        <v>0</v>
+        <v>0.016759776536312849</v>
       </c>
       <c r="AA165" s="9">
-        <v>0.040000000000000001</v>
+        <v>0.033519553072625698</v>
       </c>
       <c r="AB165" s="9">
-        <v>0.016</v>
+        <v>0.016759776536312849</v>
       </c>
       <c r="AC165" s="9">
-        <v>0</v>
+        <v>0.0111731843575419</v>
       </c>
       <c r="AD165" s="6">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AE165" s="6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AF165" s="6">
         <v>1</v>
@@ -26156,22 +26156,22 @@
         <v>0</v>
       </c>
       <c r="AH165" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI165" s="6">
         <v>0</v>
       </c>
       <c r="AJ165" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK165" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL165" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM165" s="6">
         <v>2</v>
-      </c>
-      <c r="AM165" s="6">
-        <v>0</v>
       </c>
       <c r="AN165" s="9">
         <v>0</v>
@@ -26219,7 +26219,7 @@
         <v>19954</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>51</v>
@@ -26250,31 +26250,31 @@
       </c>
       <c r="L166" s="4"/>
       <c r="M166" s="5">
-        <v>8790.8299999999999</v>
+        <v>12766.01</v>
       </c>
       <c r="N166" s="6">
-        <v>115</v>
+        <v>164</v>
       </c>
       <c r="O166" s="6">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="P166" s="7">
-        <v>5.9636901785714285</v>
+        <v>7.3983434782608697</v>
       </c>
       <c r="Q166" s="8">
-        <v>16.232352941176469</v>
+        <v>16.831746428571428</v>
       </c>
       <c r="R166" s="8">
-        <v>2.770098529411765</v>
+        <v>2.7087309523809524</v>
       </c>
       <c r="S166" s="8">
         <v>7</v>
       </c>
       <c r="T166" s="9">
-        <v>0.5</v>
+        <v>0.45238095238095238</v>
       </c>
       <c r="U166" s="9">
-        <v>0.058823529411764705</v>
+        <v>0.047619047619047616</v>
       </c>
       <c r="V166" s="9">
         <v>0</v>
@@ -26283,7 +26283,7 @@
         <v>0</v>
       </c>
       <c r="X166" s="9">
-        <v>0.014705882352941176</v>
+        <v>0.011904761904761904</v>
       </c>
       <c r="Y166" s="9">
         <v>0</v>
@@ -26295,10 +26295,10 @@
         <v>0</v>
       </c>
       <c r="AB166" s="9">
-        <v>0.014705882352941176</v>
+        <v>0.011904761904761904</v>
       </c>
       <c r="AC166" s="9">
-        <v>0.029411764705882353</v>
+        <v>0.023809523809523808</v>
       </c>
       <c r="AD166" s="6">
         <v>4</v>
@@ -26376,7 +26376,7 @@
         <v>19956</v>
       </c>
       <c r="B167" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C167" s="4">
         <v>51</v>
@@ -26407,40 +26407,40 @@
       </c>
       <c r="L167" s="4"/>
       <c r="M167" s="5">
-        <v>7392.2699999999995</v>
+        <v>10140.74</v>
       </c>
       <c r="N167" s="6">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="O167" s="6">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="P167" s="7">
-        <v>6.5905225490196075</v>
+        <v>6.7728682170542642</v>
       </c>
       <c r="Q167" s="8">
-        <v>22.917203225806453</v>
+        <v>23.965350000000001</v>
       </c>
       <c r="R167" s="8">
-        <v>10.066935483870967</v>
+        <v>10.793201315789474</v>
       </c>
       <c r="S167" s="8">
         <v>7</v>
       </c>
       <c r="T167" s="9">
-        <v>0.14516129032258066</v>
+        <v>0.11842105263157894</v>
       </c>
       <c r="U167" s="9">
-        <v>0.19047619047619047</v>
+        <v>0.18181818181818182</v>
       </c>
       <c r="V167" s="9">
-        <v>0.063492063492063489</v>
+        <v>0.07792207792207792</v>
       </c>
       <c r="W167" s="9">
         <v>0</v>
       </c>
       <c r="X167" s="9">
-        <v>0.063492063492063489</v>
+        <v>0.051948051948051951</v>
       </c>
       <c r="Y167" s="9">
         <v>0</v>
@@ -26452,19 +26452,19 @@
         <v>0</v>
       </c>
       <c r="AB167" s="9">
-        <v>0.047619047619047616</v>
+        <v>0.03896103896103896</v>
       </c>
       <c r="AC167" s="9">
-        <v>0.047619047619047616</v>
+        <v>0.03896103896103896</v>
       </c>
       <c r="AD167" s="6">
+        <v>16</v>
+      </c>
+      <c r="AE167" s="6">
         <v>14</v>
       </c>
-      <c r="AE167" s="6">
-        <v>12</v>
-      </c>
       <c r="AF167" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG167" s="6">
         <v>0</v>
@@ -26847,7 +26847,7 @@
         <v>19961</v>
       </c>
       <c r="B170" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C170" s="4">
         <v>51</v>
@@ -26878,61 +26878,61 @@
       </c>
       <c r="L170" s="4"/>
       <c r="M170" s="5">
-        <v>17046.330000000002</v>
+        <v>20939.880000000001</v>
       </c>
       <c r="N170" s="6">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="O170" s="6">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="P170" s="7">
-        <v>7.602986705202313</v>
+        <v>7.2743712264150941</v>
       </c>
       <c r="Q170" s="8">
-        <v>25.830755670103091</v>
+        <v>24.519166666666667</v>
       </c>
       <c r="R170" s="8">
-        <v>11.005730208333333</v>
+        <v>10.138515966386555</v>
       </c>
       <c r="S170" s="8">
         <v>7</v>
       </c>
       <c r="T170" s="9">
-        <v>0.23711340206185566</v>
+        <v>0.25</v>
       </c>
       <c r="U170" s="9">
-        <v>0.14432989690721648</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="V170" s="9">
-        <v>0.020618556701030927</v>
+        <v>0.016666666666666666</v>
       </c>
       <c r="W170" s="9">
         <v>0</v>
       </c>
       <c r="X170" s="9">
-        <v>0.020618556701030927</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="Y170" s="9">
-        <v>0.010309278350515464</v>
+        <v>0.0083333333333333332</v>
       </c>
       <c r="Z170" s="9">
         <v>0</v>
       </c>
       <c r="AA170" s="9">
-        <v>0.092783505154639179</v>
+        <v>0.09166666666666666</v>
       </c>
       <c r="AB170" s="9">
         <v>0</v>
       </c>
       <c r="AC170" s="9">
-        <v>0.020618556701030927</v>
+        <v>0.016666666666666666</v>
       </c>
       <c r="AD170" s="6">
+        <v>19</v>
+      </c>
+      <c r="AE170" s="6">
         <v>16</v>
-      </c>
-      <c r="AE170" s="6">
-        <v>14</v>
       </c>
       <c r="AF170" s="6">
         <v>2</v>
@@ -26941,7 +26941,7 @@
         <v>0</v>
       </c>
       <c r="AH170" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI170" s="6">
         <v>1</v>
@@ -26950,7 +26950,7 @@
         <v>0</v>
       </c>
       <c r="AK170" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AL170" s="6">
         <v>0</v>
